--- a/.agents/skills/autopaper-literature/assets/literature-index-template.xlsx
+++ b/.agents/skills/autopaper-literature/assets/literature-index-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文献清单" sheetId="1" r:id="Rb43abb662e4a4472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文献清单" sheetId="1" r:id="R84b08b4614ca4319"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -106,7 +106,7 @@
         <x:color rgb="FF2F6B2F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -117,7 +117,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -127,7 +127,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -137,7 +137,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -147,9 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiteratureTable" displayName="LiteratureTable" ref="A4:R4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:R4"/>
-  <x:tableColumns count="18">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LiteratureTable" displayName="LiteratureTable" ref="A4:U4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="21">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="目录名"/>
     <x:tableColumn id="3" name="论文题名"/>
@@ -168,6 +167,9 @@
     <x:tableColumn id="16" name="下载来源"/>
     <x:tableColumn id="17" name="首次收录时间"/>
     <x:tableColumn id="18" name="最后更新时间"/>
+    <x:tableColumn id="19" name="中科院分区"/>
+    <x:tableColumn id="20" name="影响因子（IF）"/>
+    <x:tableColumn id="21" name="分区/IF依据"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -389,6 +391,9 @@
     <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="22" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -510,6 +515,15 @@
       <x:c r="R4" s="8" t="str">
         <x:v>最后更新时间</x:v>
       </x:c>
+      <x:c r="S4" t="str">
+        <x:v>中科院分区</x:v>
+      </x:c>
+      <x:c r="T4" t="str">
+        <x:v>影响因子（IF）</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:v>分区/IF依据</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11"/>
@@ -20440,7 +20454,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74ce3a258a6547f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8eb2bec5dc44add"/>
   </x:tableParts>
 </x:worksheet>
 </file>